--- a/EvnMonitor.xlsx
+++ b/EvnMonitor.xlsx
@@ -1121,7 +1121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="42.75" spans="1:4">
+    <row r="2" ht="14.75" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="28.75" spans="1:4">
+    <row r="3" ht="14.75" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="28.75" spans="1:4">
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="42.75" spans="1:4">
+    <row r="5" ht="28.75" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="42.75" spans="1:4">
+    <row r="6" ht="28.75" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" ht="42.75" spans="1:4">
+    <row r="7" ht="28.75" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="28.75" spans="1:4">
+    <row r="8" ht="14.75" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" ht="42.75" spans="1:4">
+    <row r="9" ht="28.75" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
@@ -1233,7 +1233,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" ht="42.75" spans="1:4">
+    <row r="10" ht="14.75" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>33</v>
       </c>

--- a/EvnMonitor.xlsx
+++ b/EvnMonitor.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>模块名称</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>功能</t>
+  </si>
+  <si>
+    <t>硬件清单</t>
   </si>
   <si>
     <t>主控板</t>
@@ -778,15 +781,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1099,15 +1105,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20.5454545454545" customWidth="1"/>
     <col min="2" max="2" width="34.7272727272727" customWidth="1"/>
     <col min="4" max="4" width="18.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:4">
+    <row r="1" ht="14.75" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1120,131 +1126,155 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" ht="14.75" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" ht="14.75" spans="1:5">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" ht="14.75" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" ht="14.75" spans="1:5">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" ht="14.75" spans="1:5">
+      <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2"/>
     </row>
-    <row r="5" ht="28.75" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" ht="28.75" spans="1:5">
+      <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2"/>
     </row>
-    <row r="6" ht="28.75" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" ht="28.75" spans="1:5">
+      <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" ht="28.75" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="7" ht="28.75" spans="1:5">
+      <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" ht="14.75" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="8" ht="14.75" spans="1:5">
+      <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" ht="28.75" spans="1:4">
-      <c r="A9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="9" ht="28.75" spans="1:5">
+      <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" ht="14.75" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" ht="14.75" spans="1:5">
+      <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>36</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EvnMonitor.xlsx
+++ b/EvnMonitor.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>模块名称</t>
   </si>
@@ -41,9 +41,6 @@
   </si>
   <si>
     <t>功能</t>
-  </si>
-  <si>
-    <t>硬件清单</t>
   </si>
   <si>
     <t>主控板</t>
@@ -1113,7 +1110,7 @@
     <col min="4" max="4" width="18.5454545454545" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:5">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1126,156 +1123,142 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2"/>
     </row>
-    <row r="2" ht="14.75" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="14.75" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" ht="14.75" spans="1:5">
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" ht="28.75" spans="1:5">
       <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" ht="28.75" spans="1:5">
       <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" ht="28.75" spans="1:5">
       <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="14.75" spans="1:5">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" ht="28.75" spans="1:5">
       <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" ht="14.75" spans="1:5">
       <c r="A10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
+      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
